--- a/artfynd/A 21227-2026 artfynd.xlsx
+++ b/artfynd/A 21227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114950256</v>
+        <v>114950415</v>
       </c>
       <c r="B2" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528341</v>
+        <v>528384</v>
       </c>
       <c r="R2" t="n">
-        <v>6484643</v>
+        <v>6484703</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,6 +788,486 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114950417</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>528277</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6484708</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114950256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>528341</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6484643</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114950092</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6484605</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114950096</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528384</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6484578</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>

--- a/artfynd/A 21227-2026 artfynd.xlsx
+++ b/artfynd/A 21227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950415</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950092</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,8 +1297,20 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>